--- a/Cubs/postplanner-imports/cubs-postplanner-2026-03-28.xlsx
+++ b/Cubs/postplanner-imports/cubs-postplanner-2026-03-28.xlsx
@@ -478,7 +478,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>03/28/2026  11:22</t>
+          <t>03/28/2026  11:40</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>03/28/2026  12:32</t>
+          <t>03/28/2026  12:48</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -508,7 +508,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>03/28/2026  13:42</t>
+          <t>03/28/2026  13:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -523,7 +523,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>03/28/2026  14:52</t>
+          <t>03/28/2026  15:04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -538,7 +538,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>03/28/2026  16:02</t>
+          <t>03/28/2026  16:12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>03/28/2026  17:12</t>
+          <t>03/28/2026  17:20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -570,12 +570,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>03/28/2026  18:22</t>
+          <t>03/28/2026  18:28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cade Horton takes the mound tonight for Game 3.
+          <t>Cade Horton takes the mound tonight for Game 2.
 He went 11-4 with a 2.67 ERA as a ROOKIE in 2025. This is the guy the Cubs built around.
 Miles Mikolas better be ready. 🔥
 #Cubs #GoCubs #FlyTheW</t>
@@ -585,13 +585,13 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>03/28/2026  19:32</t>
+          <t>03/28/2026  19:36</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>First pitch in minutes.
-Cade Horton. Nationals Park. Win or go home on this road trip.
+Cade Horton. Wrigley Field. Chance to even the series at home.
 Let's go, Cubs.
 #Cubs #GoCubs #FlyTheW</t>
         </is>
@@ -600,7 +600,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>03/28/2026  20:42</t>
+          <t>03/28/2026  20:44</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
